--- a/data/trans_camb/P6901-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 14,27</t>
+          <t>-47,28; 12,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-54,35; -0,28</t>
+          <t>-54,91; -2,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,16; 30,74</t>
+          <t>8,28; 31,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 23,55</t>
+          <t>-40,61; 18,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 27,82</t>
+          <t>-14,45; 26,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,13; 8,57</t>
+          <t>-55,51; 11,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 11,0</t>
+          <t>-29,23; 10,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 1,8</t>
+          <t>-35,04; 5,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-38,1; 15,79</t>
+          <t>-42,34; 14,25</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,34; 17,54</t>
+          <t>-59,08; 16,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,56; -0,31</t>
+          <t>-64,71; -3,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 44,37</t>
+          <t>9,03; 46,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 30,84</t>
+          <t>-46,8; 23,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 38,86</t>
+          <t>-14,39; 38,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 10,42</t>
+          <t>-63,28; 13,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 13,71</t>
+          <t>-34,71; 13,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 2,51</t>
+          <t>-41,24; 6,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 19,81</t>
+          <t>-47,87; 17,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 17,75</t>
+          <t>-6,89; 16,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 22,27</t>
+          <t>-3,31; 21,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 22,76</t>
+          <t>-7,09; 22,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 18,39</t>
+          <t>-10,42; 18,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 28,8</t>
+          <t>5,35; 30,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 6,26</t>
+          <t>-26,2; 6,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 13,77</t>
+          <t>-5,27; 13,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 21,23</t>
+          <t>3,6; 21,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 11,69</t>
+          <t>-10,3; 12,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 27,32</t>
+          <t>-9,16; 24,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 34,32</t>
+          <t>-3,91; 32,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 33,7</t>
+          <t>-9,31; 32,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 27,73</t>
+          <t>-12,51; 27,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 43,51</t>
+          <t>6,98; 47,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 9,43</t>
+          <t>-33,11; 9,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 19,96</t>
+          <t>-6,66; 20,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 31,5</t>
+          <t>4,96; 31,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 16,61</t>
+          <t>-13,63; 17,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 13,98</t>
+          <t>-11,85; 15,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 20,4</t>
+          <t>-1,89; 20,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 20,61</t>
+          <t>-4,05; 20,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 12,55</t>
+          <t>-14,08; 12,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 16,02</t>
+          <t>-10,0; 15,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 11,97</t>
+          <t>-13,24; 12,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 10,42</t>
+          <t>-8,18; 10,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 16,33</t>
+          <t>-1,06; 15,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 14,03</t>
+          <t>-3,53; 13,84</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 21,8</t>
+          <t>-16,27; 25,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 33,59</t>
+          <t>-2,5; 34,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 33,21</t>
+          <t>-5,73; 31,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 17,75</t>
+          <t>-16,61; 17,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 22,64</t>
+          <t>-11,83; 21,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 17,03</t>
+          <t>-15,41; 17,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 15,08</t>
+          <t>-10,8; 14,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 24,07</t>
+          <t>-1,36; 24,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 20,53</t>
+          <t>-4,68; 20,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 10,77</t>
+          <t>-13,54; 11,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 0,74</t>
+          <t>-23,8; 2,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 1,21</t>
+          <t>-22,41; 2,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 3,46</t>
+          <t>-37,62; 3,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 14,45</t>
+          <t>-19,13; 13,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 16,66</t>
+          <t>-14,78; 17,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 5,94</t>
+          <t>-14,81; 6,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 4,57</t>
+          <t>-17,2; 2,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 7,78</t>
+          <t>-12,83; 9,47</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 15,13</t>
+          <t>-16,73; 16,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 0,8</t>
+          <t>-29,5; 2,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 1,64</t>
+          <t>-28,31; 3,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 4,59</t>
+          <t>-42,0; 3,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 19,81</t>
+          <t>-21,01; 19,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 23,66</t>
+          <t>-16,44; 25,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 7,97</t>
+          <t>-17,78; 9,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 6,17</t>
+          <t>-21,08; 4,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 10,57</t>
+          <t>-15,73; 12,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -0,86</t>
+          <t>-31,79; 0,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 4,21</t>
+          <t>-27,24; 3,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-36,79; -9,09</t>
+          <t>-34,95; -6,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 56,27</t>
+          <t>1,81; 53,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 49,64</t>
+          <t>-4,04; 49,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 49,47</t>
+          <t>-6,29; 44,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 10,4</t>
+          <t>-15,56; 10,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 10,41</t>
+          <t>-16,34; 9,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 1,46</t>
+          <t>-21,48; 1,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,54; -1,3</t>
+          <t>-34,21; -0,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 4,3</t>
+          <t>-29,07; 3,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,23; -11,37</t>
+          <t>-38,53; -8,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,96; 154,82</t>
+          <t>2,97; 132,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 130,71</t>
+          <t>-3,9; 128,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 139,12</t>
+          <t>-7,57; 113,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 13,66</t>
+          <t>-17,47; 13,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 13,18</t>
+          <t>-18,19; 12,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 2,0</t>
+          <t>-23,68; 1,07</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,26</t>
+          <t>-6,76; 5,66</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,86</t>
+          <t>-6,64; 5,08</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 3,93</t>
+          <t>-8,88; 3,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 8,13</t>
+          <t>-7,69; 7,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 14,08</t>
+          <t>-0,84; 14,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 8,01</t>
+          <t>-7,43; 8,84</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,71</t>
+          <t>-5,57; 4,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,34</t>
+          <t>-2,14; 7,26</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 5,43</t>
+          <t>-5,19; 4,5</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 7,15</t>
+          <t>-8,69; 7,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,13</t>
+          <t>-8,56; 7,08</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 5,39</t>
+          <t>-11,83; 5,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 10,99</t>
+          <t>-9,46; 9,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 19,53</t>
+          <t>-0,96; 19,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 10,79</t>
+          <t>-9,13; 12,14</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 6,4</t>
+          <t>-7,0; 5,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 9,93</t>
+          <t>-2,75; 9,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 7,37</t>
+          <t>-6,72; 5,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6901-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,86</t>
+          <t>-15,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>-2,15</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 12,92</t>
+          <t>-43,47; 15,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-54,91; -2,76</t>
+          <t>-56,44; -1,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 31,55</t>
+          <t>9,33; 31,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 18,66</t>
+          <t>-38,85; 19,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 26,41</t>
+          <t>-13,6; 28,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 11,4</t>
+          <t>-52,0; 12,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 10,78</t>
+          <t>-29,0; 11,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 5,64</t>
+          <t>-34,79; 4,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-42,34; 14,25</t>
+          <t>-34,75; 15,04</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,97%</t>
+          <t>-18,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,54%</t>
+          <t>-2,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,08; 16,86</t>
+          <t>-51,88; 18,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,71; -3,59</t>
+          <t>-65,57; -1,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 46,09</t>
+          <t>10,28; 45,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 23,45</t>
+          <t>-41,9; 23,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 38,67</t>
+          <t>-14,23; 40,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,28; 13,94</t>
+          <t>-60,01; 14,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 13,74</t>
+          <t>-33,97; 14,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 6,83</t>
+          <t>-40,17; 4,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 17,87</t>
+          <t>-40,43; 18,91</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,24</t>
+          <t>12,82</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-10,7</t>
+          <t>-9,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>3,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 16,72</t>
+          <t>-7,75; 17,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 21,29</t>
+          <t>-2,31; 21,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 22,05</t>
+          <t>-2,16; 25,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 18,27</t>
+          <t>-11,18; 17,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 30,62</t>
+          <t>3,63; 28,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 6,75</t>
+          <t>-28,01; 6,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 13,77</t>
+          <t>-4,51; 13,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 21,14</t>
+          <t>3,85; 20,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 12,15</t>
+          <t>-8,36; 13,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-14,31%</t>
+          <t>-13,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 24,79</t>
+          <t>-10,22; 27,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 32,44</t>
+          <t>-2,94; 33,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 32,46</t>
+          <t>-2,62; 37,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 27,7</t>
+          <t>-13,37; 25,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 47,94</t>
+          <t>4,57; 44,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 9,39</t>
+          <t>-34,76; 9,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 20,04</t>
+          <t>-5,76; 19,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 31,45</t>
+          <t>5,04; 30,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 17,21</t>
+          <t>-11,11; 19,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>6,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 15,45</t>
+          <t>-12,83; 12,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 20,57</t>
+          <t>-3,36; 19,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 20,56</t>
+          <t>-3,12; 19,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 12,38</t>
+          <t>-14,9; 13,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 15,58</t>
+          <t>-9,63; 17,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 12,45</t>
+          <t>-10,94; 12,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 10,3</t>
+          <t>-7,87; 10,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 15,87</t>
+          <t>-1,58; 15,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 13,84</t>
+          <t>-2,72; 13,96</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0,43%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 25,24</t>
+          <t>-16,71; 19,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 34,37</t>
+          <t>-3,9; 32,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 31,83</t>
+          <t>-4,26; 30,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 17,57</t>
+          <t>-17,78; 18,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 21,66</t>
+          <t>-11,23; 24,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 17,18</t>
+          <t>-12,74; 18,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 14,92</t>
+          <t>-10,47; 15,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 24,04</t>
+          <t>-1,87; 23,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 20,42</t>
+          <t>-3,46; 20,56</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-8,08</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-2,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-3,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 11,65</t>
+          <t>-12,73; 12,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 2,16</t>
+          <t>-23,85; 2,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 2,92</t>
+          <t>-20,72; 2,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 3,0</t>
+          <t>-37,86; 0,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 13,99</t>
+          <t>-18,66; 13,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 17,38</t>
+          <t>-14,28; 13,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 6,69</t>
+          <t>-15,49; 5,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 2,94</t>
+          <t>-17,47; 3,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 9,47</t>
+          <t>-11,81; 5,11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-14,14%</t>
+          <t>-10,55%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,76%</t>
+          <t>-3,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-3,93%</t>
+          <t>-4,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 16,43</t>
+          <t>-16,09; 18,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 2,48</t>
+          <t>-29,51; 3,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 3,5</t>
+          <t>-25,16; 3,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,0; 3,74</t>
+          <t>-42,27; 1,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 19,01</t>
+          <t>-20,91; 18,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 25,13</t>
+          <t>-15,44; 19,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 9,27</t>
+          <t>-18,56; 7,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 4,06</t>
+          <t>-21,68; 4,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 12,52</t>
+          <t>-14,12; 7,09</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-23,07</t>
+          <t>-22,38</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,54</t>
+          <t>17,05</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-10,51</t>
+          <t>-10,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 0,31</t>
+          <t>-32,28; -1,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 3,02</t>
+          <t>-27,37; 1,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,95; -6,12</t>
+          <t>-35,98; -7,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 53,71</t>
+          <t>3,16; 57,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 49,76</t>
+          <t>-3,57; 50,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 44,9</t>
+          <t>-6,78; 43,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 10,07</t>
+          <t>-17,37; 10,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 9,73</t>
+          <t>-16,55; 10,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 1,09</t>
+          <t>-20,23; 3,0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-25,45%</t>
+          <t>-24,68%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-12,44%</t>
+          <t>-12,09%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,21; -0,13</t>
+          <t>-34,63; -2,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 3,66</t>
+          <t>-29,56; 2,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,53; -8,68</t>
+          <t>-38,96; -9,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,97; 132,05</t>
+          <t>5,11; 161,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 128,72</t>
+          <t>-3,58; 151,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 113,41</t>
+          <t>-8,03; 111,84</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 13,34</t>
+          <t>-19,9; 13,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 12,17</t>
+          <t>-18,32; 13,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 1,07</t>
+          <t>-22,3; 3,97</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,66</t>
+          <t>-7,46; 5,7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,08</t>
+          <t>-6,98; 6,08</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 3,84</t>
+          <t>-6,31; 5,75</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 7,15</t>
+          <t>-8,41; 8,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 14,08</t>
+          <t>-1,15; 14,66</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 8,84</t>
+          <t>-7,17; 6,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,38</t>
+          <t>-5,67; 4,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,26</t>
+          <t>-2,77; 7,33</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 4,5</t>
+          <t>-4,46; 4,5</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-3,1%</t>
+          <t>-0,29%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>-0,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-0,74%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 7,84</t>
+          <t>-9,69; 7,73</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,08</t>
+          <t>-8,9; 8,34</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 5,18</t>
+          <t>-8,24; 7,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 9,64</t>
+          <t>-10,44; 10,94</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 19,26</t>
+          <t>-1,39; 20,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 12,14</t>
+          <t>-8,59; 8,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 5,99</t>
+          <t>-7,1; 5,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 9,87</t>
+          <t>-3,54; 9,96</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 5,99</t>
+          <t>-5,66; 6,14</t>
         </is>
       </c>
     </row>
